--- a/data/trans_dic/P16A01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A01-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,21</t>
+          <t>4,54; 9,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,24; 15,27</t>
+          <t>8,37; 14,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 12,15</t>
+          <t>5,77; 11,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,88</t>
+          <t>3,89; 8,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 12,01</t>
+          <t>5,9; 12,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 12,08</t>
+          <t>5,61; 12,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,93</t>
+          <t>4,43; 10,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,5</t>
+          <t>5,65; 9,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 9,27</t>
+          <t>5,55; 9,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,06; 12,78</t>
+          <t>7,93; 12,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 10,07</t>
+          <t>5,92; 9,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 8,42</t>
+          <t>5,18; 8,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 10,37</t>
+          <t>4,43; 9,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,68</t>
+          <t>4,59; 10,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 10,87</t>
+          <t>4,95; 10,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 11,53</t>
+          <t>6,17; 11,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 10,68</t>
+          <t>5,25; 10,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 13,08</t>
+          <t>6,41; 12,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 12,41</t>
+          <t>6,44; 12,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,3</t>
+          <t>4,88; 9,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,06</t>
+          <t>5,47; 9,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 10,62</t>
+          <t>6,08; 10,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,65</t>
+          <t>6,32; 10,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 9,65</t>
+          <t>6,23; 9,73</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,54</t>
+          <t>5,57; 10,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 11,53</t>
+          <t>6,48; 11,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 11,3</t>
+          <t>6,53; 11,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 10,41</t>
+          <t>2,19; 10,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 15,76</t>
+          <t>6,32; 16,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 11,33</t>
+          <t>4,8; 12,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 15,52</t>
+          <t>5,62; 15,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 14,96</t>
+          <t>7,22; 14,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 10,93</t>
+          <t>6,36; 10,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,55</t>
+          <t>6,65; 10,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,09</t>
+          <t>6,8; 11,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,55</t>
+          <t>2,67; 10,46</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 8,46</t>
+          <t>5,63; 8,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,89</t>
+          <t>8,21; 11,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 9,59</t>
+          <t>6,45; 9,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,34</t>
+          <t>5,48; 9,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,04</t>
+          <t>5,17; 8,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,89</t>
+          <t>8,16; 12,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 9,56</t>
+          <t>6,14; 9,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,86</t>
+          <t>2,35; 6,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,23</t>
+          <t>5,9; 8,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 11,75</t>
+          <t>8,72; 11,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 9,23</t>
+          <t>6,59; 9,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,54</t>
+          <t>4,39; 7,46</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,17</t>
+          <t>4,98; 10,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 11,57</t>
+          <t>6,84; 11,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,2</t>
+          <t>5,01; 9,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,77</t>
+          <t>4,5; 9,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,95</t>
+          <t>3,83; 7,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,18</t>
+          <t>5,44; 9,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 10,41</t>
+          <t>6,31; 10,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,13; 10,37</t>
+          <t>6,23; 10,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,11</t>
+          <t>4,62; 7,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,66</t>
+          <t>6,57; 9,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,17</t>
+          <t>6,36; 9,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 9,26</t>
+          <t>6,08; 9,34</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,91</t>
+          <t>3,54; 9,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,8; 14,37</t>
+          <t>6,71; 14,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,19; 9,67</t>
+          <t>3,93; 9,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,91</t>
+          <t>0,56; 5,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,04; 6,39</t>
+          <t>4,01; 6,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,6</t>
+          <t>6,06; 9,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,31; 11,16</t>
+          <t>7,37; 11,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,85</t>
+          <t>5,25; 8,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,31</t>
+          <t>4,01; 6,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,6; 9,63</t>
+          <t>6,76; 9,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,17</t>
+          <t>7,05; 10,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,29</t>
+          <t>4,38; 7,44</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 7,89</t>
+          <t>6,02; 7,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 10,42</t>
+          <t>8,38; 10,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,78</t>
+          <t>6,83; 8,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 7,58</t>
+          <t>4,93; 7,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 7,41</t>
+          <t>5,67; 7,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 9,29</t>
+          <t>7,51; 9,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,34</t>
+          <t>7,49; 9,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,96</t>
+          <t>5,65; 7,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,08; 7,3</t>
+          <t>6,02; 7,26</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,2; 9,59</t>
+          <t>8,22; 9,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,33; 8,66</t>
+          <t>7,39; 8,73</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 7,5</t>
+          <t>5,73; 7,51</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20687; 43619</t>
+          <t>21514; 43863</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36006; 66750</t>
+          <t>36603; 64579</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25448; 52147</t>
+          <t>24762; 48579</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19931; 44838</t>
+          <t>19657; 44637</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16981; 36843</t>
+          <t>18102; 37212</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17558; 37990</t>
+          <t>17626; 37972</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15179; 34448</t>
+          <t>15384; 35096</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24978; 42505</t>
+          <t>25298; 43737</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42401; 72382</t>
+          <t>43352; 72320</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60562; 96047</t>
+          <t>59613; 96076</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46178; 78187</t>
+          <t>45936; 77147</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49242; 80237</t>
+          <t>49365; 81261</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16671; 38036</t>
+          <t>16266; 36183</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20379; 44550</t>
+          <t>19159; 43446</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18566; 40996</t>
+          <t>18667; 40576</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26513; 52146</t>
+          <t>27900; 53698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19133; 39733</t>
+          <t>19508; 40700</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20958; 43856</t>
+          <t>21508; 43039</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22429; 46206</t>
+          <t>23987; 46808</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18986; 35523</t>
+          <t>18626; 34916</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39553; 66949</t>
+          <t>40446; 69045</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47151; 79900</t>
+          <t>45754; 79185</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47731; 79792</t>
+          <t>47353; 75797</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51177; 80475</t>
+          <t>51953; 81130</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31750; 57144</t>
+          <t>30190; 56554</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41118; 72217</t>
+          <t>40565; 69724</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32848; 58965</t>
+          <t>34095; 59355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14244; 69553</t>
+          <t>14629; 69428</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10085; 26450</t>
+          <t>10601; 28063</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12617; 29221</t>
+          <t>12389; 31429</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9341; 25779</t>
+          <t>9340; 25890</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12212; 24974</t>
+          <t>12056; 24705</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45472; 77626</t>
+          <t>45141; 75503</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57750; 93312</t>
+          <t>58841; 93049</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47288; 76326</t>
+          <t>46753; 77162</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24922; 88120</t>
+          <t>22274; 87364</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70294; 104741</t>
+          <t>69739; 104425</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93146; 137578</t>
+          <t>95033; 138764</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73822; 110198</t>
+          <t>74134; 112492</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55921; 96602</t>
+          <t>56707; 97535</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38016; 64547</t>
+          <t>36923; 63853</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>62743; 98815</t>
+          <t>62548; 96975</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49984; 78913</t>
+          <t>50743; 82132</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25426; 66991</t>
+          <t>22968; 66734</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>115885; 160697</t>
+          <t>115155; 160656</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>167777; 226049</t>
+          <t>167718; 222799</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>131605; 182430</t>
+          <t>130173; 178671</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>86973; 151700</t>
+          <t>88241; 150038</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16896; 35532</t>
+          <t>17401; 35441</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34739; 59086</t>
+          <t>34945; 60944</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31689; 57126</t>
+          <t>31101; 57225</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19315; 41556</t>
+          <t>21309; 44649</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20767; 45233</t>
+          <t>21760; 44620</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40819; 69535</t>
+          <t>41196; 68856</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46346; 76848</t>
+          <t>46551; 77988</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>51420; 87016</t>
+          <t>52241; 88838</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44614; 74455</t>
+          <t>42430; 72708</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81988; 122472</t>
+          <t>83276; 119750</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84985; 124643</t>
+          <t>86404; 124986</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79526; 121531</t>
+          <t>79894; 122674</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10405; 26571</t>
+          <t>10546; 27199</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18072; 38197</t>
+          <t>17840; 39620</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12040; 27776</t>
+          <t>11274; 28412</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1231; 14221</t>
+          <t>1339; 13820</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50469; 79743</t>
+          <t>50137; 79730</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68436; 106055</t>
+          <t>67021; 103102</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79122; 120776</t>
+          <t>79755; 121110</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>39448; 67276</t>
+          <t>39900; 68229</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64323; 97625</t>
+          <t>62062; 98118</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>90483; 132021</t>
+          <t>92697; 136158</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96094; 139302</t>
+          <t>96512; 140425</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>43516; 72986</t>
+          <t>43821; 74485</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>199591; 257786</t>
+          <t>196942; 255933</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>286188; 355713</t>
+          <t>285970; 358663</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>230994; 297200</t>
+          <t>231197; 294223</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>169644; 255994</t>
+          <t>166352; 254657</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>192203; 250444</t>
+          <t>191521; 246866</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>261614; 328685</t>
+          <t>265768; 330987</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>263670; 329986</t>
+          <t>264529; 327780</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>202703; 284359</t>
+          <t>201705; 283143</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>403867; 485389</t>
+          <t>400404; 482527</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>570034; 666341</t>
+          <t>571536; 670424</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>506717; 599253</t>
+          <t>511099; 604067</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>401452; 521347</t>
+          <t>398232; 521502</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A01-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,26</t>
+          <t>4,49; 9,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,37; 14,77</t>
+          <t>8,53; 15,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 11,32</t>
+          <t>5,96; 11,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,84</t>
+          <t>3,8; 8,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 12,13</t>
+          <t>5,84; 12,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 12,08</t>
+          <t>5,6; 12,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 10,11</t>
+          <t>4,28; 9,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,77</t>
+          <t>5,45; 9,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,27</t>
+          <t>5,44; 9,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,78</t>
+          <t>7,63; 12,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,94</t>
+          <t>5,77; 9,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,53</t>
+          <t>5,02; 7,98</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 9,86</t>
+          <t>3,94; 9,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,42</t>
+          <t>4,76; 10,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 10,76</t>
+          <t>4,88; 10,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 11,87</t>
+          <t>6,17; 11,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,94</t>
+          <t>5,18; 11,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 12,84</t>
+          <t>6,51; 13,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 12,57</t>
+          <t>6,1; 12,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 9,15</t>
+          <t>4,66; 8,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,35</t>
+          <t>5,34; 9,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,53</t>
+          <t>6,41; 10,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 10,11</t>
+          <t>6,48; 10,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,73</t>
+          <t>5,68; 9,2</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 10,43</t>
+          <t>5,71; 10,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 11,13</t>
+          <t>6,77; 11,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 11,37</t>
+          <t>6,46; 11,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 10,39</t>
+          <t>6,83; 12,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 16,73</t>
+          <t>6,09; 16,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 12,18</t>
+          <t>4,66; 11,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 15,58</t>
+          <t>5,32; 15,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 14,8</t>
+          <t>7,82; 15,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,63</t>
+          <t>6,53; 11,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,52</t>
+          <t>6,53; 10,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 11,21</t>
+          <t>6,75; 11,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 10,46</t>
+          <t>7,56; 12,0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,43</t>
+          <t>5,77; 8,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 9,79</t>
+          <t>6,37; 9,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,43</t>
+          <t>6,01; 9,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 8,94</t>
+          <t>5,29; 8,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 12,65</t>
+          <t>8,2; 12,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 9,94</t>
+          <t>5,91; 9,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,83</t>
+          <t>4,97; 7,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,23</t>
+          <t>5,88; 8,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 11,58</t>
+          <t>8,66; 11,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,59; 9,04</t>
+          <t>6,58; 9,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,46</t>
+          <t>5,86; 8,28</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,14</t>
+          <t>4,84; 10,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,94</t>
+          <t>6,81; 11,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,22</t>
+          <t>5,12; 9,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 9,42</t>
+          <t>4,33; 8,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,85</t>
+          <t>3,76; 8,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 9,09</t>
+          <t>5,4; 9,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,56</t>
+          <t>6,24; 10,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 10,59</t>
+          <t>8,02; 11,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,92</t>
+          <t>4,87; 8,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 9,45</t>
+          <t>6,61; 9,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,2</t>
+          <t>6,23; 9,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,34</t>
+          <t>7,03; 9,9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,12</t>
+          <t>3,47; 8,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,71; 14,9</t>
+          <t>6,77; 14,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,93; 9,89</t>
+          <t>3,87; 9,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,75</t>
+          <t>0,9; 8,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,01; 6,38</t>
+          <t>3,99; 6,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,06; 9,33</t>
+          <t>6,26; 9,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,37; 11,19</t>
+          <t>7,27; 11,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,98</t>
+          <t>5,18; 8,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,01; 6,34</t>
+          <t>4,17; 6,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,76; 9,93</t>
+          <t>6,79; 9,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,26</t>
+          <t>7,09; 10,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,44</t>
+          <t>4,62; 7,69</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,83</t>
+          <t>6,03; 7,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 10,5</t>
+          <t>8,39; 10,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,83; 8,69</t>
+          <t>6,81; 8,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,55</t>
+          <t>6,15; 8,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,31</t>
+          <t>5,62; 7,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 9,36</t>
+          <t>7,43; 9,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,49; 9,28</t>
+          <t>7,42; 9,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,93</t>
+          <t>6,78; 8,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,26</t>
+          <t>6,03; 7,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,22; 9,64</t>
+          <t>8,13; 9,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,73</t>
+          <t>7,35; 8,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 7,51</t>
+          <t>6,63; 7,9</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33239</t>
+          <t>35452</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63375</t>
+          <t>66050</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21514; 43863</t>
+          <t>21255; 43486</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36603; 64579</t>
+          <t>37310; 66818</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24762; 48579</t>
+          <t>25568; 49191</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19657; 44637</t>
+          <t>20930; 46711</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18102; 37212</t>
+          <t>17922; 37323</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17626; 37972</t>
+          <t>17623; 38119</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15384; 35096</t>
+          <t>14863; 33829</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25298; 43737</t>
+          <t>26628; 44624</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43352; 72320</t>
+          <t>42452; 72073</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59613; 96076</t>
+          <t>57337; 95424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45936; 77147</t>
+          <t>44795; 76649</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49365; 81261</t>
+          <t>52126; 82895</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>40791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26235</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64986</t>
+          <t>67793</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16266; 36183</t>
+          <t>14442; 34237</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19159; 43446</t>
+          <t>19845; 43695</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18667; 40576</t>
+          <t>18417; 39667</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27900; 53698</t>
+          <t>29819; 55190</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19508; 40700</t>
+          <t>19247; 40928</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21508; 43039</t>
+          <t>21837; 44617</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23987; 46808</t>
+          <t>22694; 45822</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18626; 34916</t>
+          <t>19693; 37684</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40446; 69045</t>
+          <t>39451; 69320</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45754; 79185</t>
+          <t>48205; 80322</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47353; 75797</t>
+          <t>48578; 80669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51953; 81130</t>
+          <t>51425; 83295</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40394</t>
+          <t>42947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17627</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58021</t>
+          <t>63491</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30190; 56554</t>
+          <t>30943; 55796</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40565; 69724</t>
+          <t>42376; 72110</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34095; 59355</t>
+          <t>33726; 58796</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14629; 69428</t>
+          <t>32228; 57215</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10601; 28063</t>
+          <t>10226; 27763</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12389; 31429</t>
+          <t>12032; 30420</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9340; 25890</t>
+          <t>8843; 25260</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12056; 24705</t>
+          <t>14666; 28432</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45141; 75503</t>
+          <t>46393; 78586</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58841; 93049</t>
+          <t>57749; 94265</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46753; 77162</t>
+          <t>46423; 76779</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22274; 87364</t>
+          <t>49811; 79110</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73570</t>
+          <t>85250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49266</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>122837</t>
+          <t>138743</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69739; 104425</t>
+          <t>71394; 105230</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95033; 138764</t>
+          <t>95032; 138723</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74134; 112492</t>
+          <t>73254; 111011</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56707; 97535</t>
+          <t>68039; 109207</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36923; 63853</t>
+          <t>37814; 64104</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>62548; 96975</t>
+          <t>62851; 96649</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50743; 82132</t>
+          <t>48796; 79758</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22968; 66734</t>
+          <t>42777; 66393</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>115155; 160656</t>
+          <t>114832; 159433</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>167718; 222799</t>
+          <t>166644; 221061</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>130173; 178671</t>
+          <t>129982; 180281</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88241; 150038</t>
+          <t>116665; 164964</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29974</t>
+          <t>34903</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>71232</t>
+          <t>81347</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>101206</t>
+          <t>116250</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17401; 35441</t>
+          <t>16920; 35468</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34945; 60944</t>
+          <t>34767; 60386</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31101; 57225</t>
+          <t>31755; 57907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21309; 44649</t>
+          <t>24575; 49503</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21760; 44620</t>
+          <t>21399; 45540</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41196; 68856</t>
+          <t>40910; 68522</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46551; 77988</t>
+          <t>46078; 76213</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52241; 88838</t>
+          <t>66554; 99073</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42430; 72708</t>
+          <t>44731; 73558</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83276; 119750</t>
+          <t>83828; 120060</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86404; 124986</t>
+          <t>84718; 125978</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79894; 122674</t>
+          <t>98181; 138301</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>51842</t>
+          <t>56259</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56526</t>
+          <t>63324</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10546; 27199</t>
+          <t>10345; 25479</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17840; 39620</t>
+          <t>17985; 38460</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11274; 28412</t>
+          <t>11122; 28466</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1339; 13820</t>
+          <t>2125; 19102</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50137; 79730</t>
+          <t>49832; 80685</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67021; 103102</t>
+          <t>69217; 103554</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79755; 121110</t>
+          <t>78703; 121414</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>39900; 68229</t>
+          <t>43652; 73659</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>62062; 98118</t>
+          <t>64497; 100354</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>92697; 136158</t>
+          <t>93107; 133809</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96512; 140425</t>
+          <t>97136; 139422</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>43821; 74485</t>
+          <t>49953; 83093</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>217510</t>
+          <t>241554</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>249441</t>
+          <t>274098</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>466951</t>
+          <t>515652</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>196942; 255933</t>
+          <t>197115; 255430</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>285970; 358663</t>
+          <t>286625; 361317</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>231197; 294223</t>
+          <t>230651; 293182</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>166352; 254657</t>
+          <t>211490; 280429</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>191521; 246866</t>
+          <t>189962; 246024</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>265768; 330987</t>
+          <t>262811; 328464</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>264529; 327780</t>
+          <t>261890; 326952</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>201705; 283143</t>
+          <t>246388; 300973</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>400404; 482527</t>
+          <t>400814; 483236</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>571536; 670424</t>
+          <t>565237; 667959</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>511099; 604067</t>
+          <t>508294; 602082</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>398232; 521502</t>
+          <t>468952; 559001</t>
         </is>
       </c>
     </row>
